--- a/artfynd/A 30862-2021 artfynd.xlsx
+++ b/artfynd/A 30862-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30862-2021 artfynd.xlsx
+++ b/artfynd/A 30862-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>94832408</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>367553.6134504232</v>
+        <v>367554</v>
       </c>
       <c r="R2" t="n">
-        <v>6323577.581511863</v>
+        <v>6323578</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,12 +777,7 @@
         <v>94832278</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>367570.1780678819</v>
+        <v>367571</v>
       </c>
       <c r="R3" t="n">
-        <v>6323617.887743859</v>
+        <v>6323618</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
